--- a/artfynd/A 44505-2023 artfynd.xlsx
+++ b/artfynd/A 44505-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44505-2023 artfynd.xlsx
+++ b/artfynd/A 44505-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88767582</v>
+        <v>98361483</v>
       </c>
       <c r="B7" t="n">
-        <v>95511</v>
+        <v>96367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,37 +1346,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221944</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fd Sandbysjön, Upl</t>
+          <t>Dängnäs, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640805.7981289383</v>
+        <v>640819.5628634617</v>
       </c>
       <c r="R7" t="n">
-        <v>6708811.793871215</v>
+        <v>6708838.968598619</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1404,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-04-02</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1410,17 +1414,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-04-02</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>noterat</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1435,22 +1434,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98361483</v>
+        <v>98361517</v>
       </c>
       <c r="B8" t="n">
-        <v>96367</v>
+        <v>96356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1463,26 +1466,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1491,13 +1494,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640819.5628634617</v>
+        <v>640797.0600137895</v>
       </c>
       <c r="R8" t="n">
-        <v>6708838.968598619</v>
+        <v>6708744.363084937</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1567,10 +1570,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98361517</v>
+        <v>88767711</v>
       </c>
       <c r="B9" t="n">
-        <v>96356</v>
+        <v>96239</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1583,38 +1586,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dängnäs, Upl</t>
+          <t>Fd Sandbysjön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640797.0600137895</v>
+        <v>640799.0225671615</v>
       </c>
       <c r="R9" t="n">
-        <v>6708744.363084937</v>
+        <v>6708770.091890812</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1641,7 +1649,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-07-06</t>
+          <t>2020-06-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1671,23 +1679,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventering inför områdesskydd - länstyrelsen Uppsala</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88767711</v>
+        <v>88767712</v>
       </c>
       <c r="B10" t="n">
         <v>96239</v>
@@ -1722,7 +1726,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1736,10 +1740,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640799.0225671615</v>
+        <v>640781.7766989917</v>
       </c>
       <c r="R10" t="n">
-        <v>6708770.091890812</v>
+        <v>6708806.911751753</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1805,127 +1809,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>88767712</v>
-      </c>
-      <c r="B11" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>504</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Fd Sandbysjön, Upl</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>640781.7766989917</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6708806.911751753</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2020-06-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2020-06-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
